--- a/scripts/clause_bank.xlsx
+++ b/scripts/clause_bank.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PDrive\My files\Docs\LF\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42499132-6ABF-40B2-AA89-7DF9D457DC10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_B26D162969248EF486F11BDD77504A0FA8538FBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{126BFD00-055F-4329-B950-75E54F7A851F}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="24450" windowHeight="16290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3680" yWindow="3740" windowWidth="28800" windowHeight="15370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Read Me First" sheetId="1" r:id="rId1"/>
@@ -25,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="370">
   <si>
     <t>Digital Content Licensing Clause Bank for Libraries</t>
   </si>
@@ -216,7 +211,7 @@
     <t>Grants tied to a specific platform that the vendor can change or sunset. 'Solely' and 'expressly' as restrictive qualifiers that foreclose reasonable implied uses. 'No other rights granted by implication' language that purports to override fair use. Revocability provisions that give the vendor unilateral control over the license. Provisions that purport to apply to the library's owned physical collection.</t>
   </si>
   <si>
-    <t>Section 1.1</t>
+    <t>Section 1.1 (The Frame of the Grant)</t>
   </si>
   <si>
     <t>M</t>
@@ -243,7 +238,7 @@
     <t>Definitions limited to 'registered' or 'current' patrons that exclude walk-ins. Definitions limited to 'on-premises' access. Requirements that users agree to vendor terms of service that may conflict with library policies. Unlimited liability for user conduct. Vendor-side termination rights for individual users without notice or cause.</t>
   </si>
   <si>
-    <t>Section 1.2</t>
+    <t>Section 1.2 (Who and Where)</t>
   </si>
   <si>
     <t>H</t>
@@ -270,9 +265,6 @@
     <t>Schedules that list specific addresses without provision for adding new ones. Per-location or per-branch fees tied to access. Remote access tied to a single authentication method controlled by the vendor. Geographic restrictions on patron access that conflict with library service mandates.</t>
   </si>
   <si>
-    <t>Section 1.3</t>
-  </si>
-  <si>
     <t>GS-PU</t>
   </si>
   <si>
@@ -297,7 +289,7 @@
     <t>Permitted uses limited to 'view only' or 'personal reference only.' Prohibitions on download or print that block ordinary library use. Definitions of 'commercial use' broad enough to cover ordinary library operations. Material breach language attached to use restrictions that creates outsize exposure for routine patron behavior.</t>
   </si>
   <si>
-    <t>Section 1.4</t>
+    <t>Section 1.3 (What Patrons Can Do)</t>
   </si>
   <si>
     <t>GS-AT</t>
@@ -324,9 +316,6 @@
     <t>Mandatory branded citation formats. Permission requirements buried in Terms of Use incorporated by reference. Per-citation fees framed as royalties. Language that purports to override applicable copyright exceptions.</t>
   </si>
   <si>
-    <t>Section 5.1</t>
-  </si>
-  <si>
     <t>GS-IL</t>
   </si>
   <si>
@@ -351,7 +340,7 @@
     <t>Outright prohibitions on ILL. Restrictions to print-only ILL that conflict with current ILL practice. Definitions of 'systematic' that capture ordinary ILL volume. Statutory damages or material breach language attached to ILL. Upstream constraints flagged by the vendor as preventing ILL; ask which specific content is constrained and why.</t>
   </si>
   <si>
-    <t>Section 1.5</t>
+    <t>Section 1.4 (Library-Specific Operations)</t>
   </si>
   <si>
     <t>GS-TDM</t>
@@ -377,9 +366,6 @@
     <t>Definitions of TDM that exclude indexing and discovery (which most libraries need). API-gated TDM that gives the vendor control over performance. Prohibitions on retention of derived data that block reproducibility. Broad vendor AI training rights buried in data use clauses elsewhere in the agreement. Definitions of 'service improvement' broad enough to cover AI training. Vendor data ownership claims that survive termination. Statutory damages language attached to TDM prohibitions.</t>
   </si>
   <si>
-    <t>Section 1.6</t>
-  </si>
-  <si>
     <t>GS-AF</t>
   </si>
   <si>
@@ -403,9 +389,6 @@
     <t>Disclaimers of accessibility obligations. Accommodation processes that route through the vendor and require individual approval. Restrictions on format-shifting that conflict with copyright accessibility exceptions. VPATs that are outdated or that disclose substantial conformance gaps without remediation commitments. WCAG conformance promised at Level A (which is insufficient) rather than AA.</t>
   </si>
   <si>
-    <t>Section 1.7</t>
-  </si>
-  <si>
     <t>GS-PR</t>
   </si>
   <si>
@@ -427,9 +410,6 @@
     <t>Prohibitions on any local copies. Restrictions to vendor-only preservation. Requirements that preservation copies be destroyed at termination. Definitions of preservation that exclude established library preservation services. Upstream rights flagged as preventing preservation deposits.</t>
   </si>
   <si>
-    <t>Section 1.8</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Access and Continuity</t>
   </si>
   <si>
@@ -460,7 +440,7 @@
     <t>Perpetual access granted only to a vendor platform that can sunset. Uncapped maintenance fees. Carve-outs for content the vendor 'no longer has rights to,' which can grow over time. Missing successor and acquisition language. Definitions of Licensed Content that exclude updates or supplements. Upstream constraints invoked without specificity; ask the vendor to identify which content is affected and why.</t>
   </si>
   <si>
-    <t>Section 2.1</t>
+    <t>Section 2.1 (Perpetual Access)</t>
   </si>
   <si>
     <t>AC-SL</t>
@@ -487,7 +467,7 @@
     <t>'Commercially reasonable efforts' as the only standard. Maintenance windows that allow extended or repeated downtime. Force majeure exclusions that are broad enough to cover most failures. Reporting available only on request rather than proactively. Service credits as the sole remedy with no escalation to termination.</t>
   </si>
   <si>
-    <t>Section 2.2</t>
+    <t>Section 2.2 (Operational Continuity)</t>
   </si>
   <si>
     <t>AC-CC</t>
@@ -514,9 +494,6 @@
     <t>Unilateral removal rights with no notice. No substitution obligation. No remedy for material removals. Legal compulsion exceptions that swallow the notice rule. 'Material' definitions that are vague enough to allow significant removals before any obligation triggers.</t>
   </si>
   <si>
-    <t>Section 2.3</t>
-  </si>
-  <si>
     <t>AC-PM</t>
   </si>
   <si>
@@ -541,9 +518,6 @@
     <t>Unilateral migration rights with no notice or cost allocation. Assignment rights with no consent or notice requirement. Successor obligations that exclude perpetual access or other long-term commitments. Force majeure or sole discretion language that covers business decisions rather than uncontrollable events.</t>
   </si>
   <si>
-    <t>Section 2.4</t>
-  </si>
-  <si>
     <t>AC-SSO</t>
   </si>
   <si>
@@ -568,9 +542,6 @@
     <t>Proprietary authentication required as the only method. Additional fees for standard library authentication tools. Integration support priced separately or unavailable. Restrictions on the use of EZproxy or other common library authentication tools.</t>
   </si>
   <si>
-    <t>Section 2.5</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Financial Terms</t>
   </si>
   <si>
@@ -601,7 +572,7 @@
     <t>Escalators tied to vendor discretion. Escalators tied to obscure indexes that are not readily verifiable. Notice periods too short to allow procurement response. Acceptance-by-continued-use mechanisms that lock in increases without renegotiation. Schedule references to fee amounts that are not actually set in the schedule.</t>
   </si>
   <si>
-    <t>Section 3.1</t>
+    <t>Section 3.1 (Fees and Escalators)</t>
   </si>
   <si>
     <t>FT-PT</t>
@@ -628,7 +599,7 @@
     <t>Payment terms shorter than the library's actual processing cycle. Suspension rights without notice. Suspension rights triggered by disputed amounts. Interest rates above local maximum. Invoice requirements that do not accommodate purchase orders or procurement coding.</t>
   </si>
   <si>
-    <t>Section 3.2</t>
+    <t>Section 3.2 (Payment Terms and Invoicing)</t>
   </si>
   <si>
     <t>FT-PX</t>
@@ -652,7 +623,7 @@
     <t>Broad confidentiality clauses elsewhere in the agreement that prevent libraries from comparing pricing across institutions. Definitions of 'comparable' libraries that are narrow enough to capture nothing. Adjustment mechanisms that defer entirely to vendor discretion.</t>
   </si>
   <si>
-    <t>Section 3.3</t>
+    <t>Section 3.3 (Pricing Transparency)</t>
   </si>
   <si>
     <t xml:space="preserve">  Data and Privacy</t>
@@ -695,7 +666,7 @@
     <t>Privacy Policies incorporated by reference and modifiable by the vendor. Definitions of 'aggregate' or 'deidentified' that allow re-identification. Carve-outs for 'service providers' or 'affiliates' that swallow the no-sharing rule. Marketing and product development purposes embedded in long lists of permitted uses. AI training listed alongside ordinary operational uses. Subpoena and legal process responses that do not require notice to the library. Breach notification timeframes longer than what state law requires for libraries. Data rights surviving termination.</t>
   </si>
   <si>
-    <t>Section 4.1</t>
+    <t>Section 4.1 (The Consolidated Privacy Clause)</t>
   </si>
   <si>
     <t>DP-SC</t>
@@ -725,7 +696,7 @@
     <t>'Commercially reasonable' security as the only standard. No specific notification timing. Security obligations subject to the general limitation of liability. Vendor right to determine when notification is 'appropriate.' Carve-outs for incidents 'caused by third parties' that excuse the vendor for service provider failures.</t>
   </si>
   <si>
-    <t>Section 4.2</t>
+    <t>Section 4.2 (Security and Patron-Created Content)</t>
   </si>
   <si>
     <t>DP-LC</t>
@@ -752,9 +723,6 @@
     <t>Vendor ownership of user-created content. Assignment of rights without specific user consent. No export functionality. Use rights extending to marketing or sale. Definitions of 'user-created content' broad enough to capture ordinary search activity.</t>
   </si>
   <si>
-    <t>Section 5.2</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Risk Allocation</t>
   </si>
   <si>
@@ -785,7 +753,7 @@
     <t>Comprehensive 'as is' and 'as available' disclaimers in all-capital text. Disclaimer of non-infringement, which leaves the licensee carrying the IP risk for the vendor's content. Disclaimer of compliance with law, which conflicts with regulatory obligations. 'To Licensor's knowledge' qualifiers on every representation.</t>
   </si>
   <si>
-    <t>Section 6.1</t>
+    <t>Section 5.1 (What the Vendor Is Promising)</t>
   </si>
   <si>
     <t>RA-IN</t>
@@ -809,7 +777,7 @@
     <t>One-way indemnification running from licensee to licensor. Indemnification capped at trivial amounts while licensee obligations remain uncapped. Carve-outs that swallow the rule ('Licensor indemnifies for infringement, except for claims arising out of Licensee's use'). Sole control of defense by the vendor, including settlement rights binding on the licensee.</t>
   </si>
   <si>
-    <t>Section 6.2</t>
+    <t>Section 5.2 (Indemnification and Limitation of Liability)</t>
   </si>
   <si>
     <t>RA-LL</t>
@@ -833,9 +801,6 @@
     <t>Caps tied to short periods (one month, three months) that effectively eliminate damages exposure. Caps that apply to indemnification obligations, which collapses indemnification protection. No carve-outs for data or IP. Consequential damages disclaimers that apply to indemnification claims, which similarly collapses the protection. Mutual caps that look fair but create unequal exposure due to differing risk profiles. Vendors that accept the cap structure but resist uncapped exposure specifically for data and privacy breaches; the next move is a separate higher cap for that category rather than collapsing it into the general cap.</t>
   </si>
   <si>
-    <t>Section 6.3</t>
-  </si>
-  <si>
     <t>RA-IS</t>
   </si>
   <si>
@@ -860,7 +825,7 @@
     <t>Permissive language ('may maintain') rather than mandatory. No cyber liability requirement. No certificate of insurance requirement. Tail coverage missing for professional liability. Coverage limits well below the realistic exposure from a data breach.</t>
   </si>
   <si>
-    <t>Section 6.4</t>
+    <t>Section 5.3 (Other Risk Provisions)</t>
   </si>
   <si>
     <t>RA-FM</t>
@@ -884,9 +849,6 @@
     <t>Broad lists including ordinary business risks (software defects, cyber attacks, supplier failures). Vendor discretion in determining what constitutes force majeure. No notice requirement. No termination right for extended events. No refund obligation for non-performance.</t>
   </si>
   <si>
-    <t>Section 6.5</t>
-  </si>
-  <si>
     <t>RA-TM</t>
   </si>
   <si>
@@ -911,9 +873,6 @@
     <t>One-way licenses running from licensee to licensor. Perpetual licenses surviving termination. Use rights for marketing, press releases, and case studies without consent. Definitions of 'public use' that include website customer lists and similar.</t>
   </si>
   <si>
-    <t>Section 5.3</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Term and Exit</t>
   </si>
   <si>
@@ -944,7 +903,7 @@
     <t>Auto-renewal at vendor's then-current fees and terms. Non-renewal notice periods of six months or longer. Auto-renewal for terms longer than one year. Notice requirements that are easy to miss. Renewal terms that incorporate vendor changes by reference.</t>
   </si>
   <si>
-    <t>Section 7.1</t>
+    <t>Section 6.1 (Term, Renewal, and Termination)</t>
   </si>
   <si>
     <t>TE-TC</t>
@@ -972,9 +931,6 @@
     <t>Asymmetric cure periods (longer for licensee than for vendor). Vendor sole discretion on materiality. Immediate termination without notice. No carve-out for disputed amounts in nonpayment termination. Forfeiture of all paid fees on termination. Termination consequences that affect perpetual access rights for content already paid for. Notice periods too short to complete library payment processes.</t>
   </si>
   <si>
-    <t>Section 7.2</t>
-  </si>
-  <si>
     <t>TE-TV</t>
   </si>
   <si>
@@ -996,9 +952,6 @@
     <t>Asymmetric convenience termination rights (vendor for convenience, licensee for cause only). Notice periods that vary by party. No pro-rata refund obligations. Termination effects extending to perpetual access rights. Vendor unilateral termination during the initial Term.</t>
   </si>
   <si>
-    <t>Section 7.3</t>
-  </si>
-  <si>
     <t>TE-AC2</t>
   </si>
   <si>
@@ -1023,7 +976,7 @@
     <t>One-way assignment rights for the vendor. Vendor sole discretion on licensee assignments. No successor assumption requirement. No notice requirement for vendor assignment. No carve-out for library system consolidation or government reorganization.</t>
   </si>
   <si>
-    <t>Section 7.4</t>
+    <t>Section 6.2 (Assignment and Change of Control)</t>
   </si>
   <si>
     <t xml:space="preserve">  Dispute Resolution</t>
@@ -1056,7 +1009,7 @@
     <t>Choice of law combined with venue that strips away local protections. Mandatory arbitration paired with remote venue. Class action and jury trial waivers (often grouped with venue clauses). Waivers of sovereign or governmental immunity (which may be impermissible for public licensees regardless of contract language).</t>
   </si>
   <si>
-    <t>Section 8.1</t>
+    <t>Section 7.1 (Governing Law and Venue)</t>
   </si>
   <si>
     <t>DR-DR2</t>
@@ -1080,7 +1033,7 @@
     <t>Mandatory arbitration in any form. Vendor-chosen arbitration providers. Arbitration venue in vendor's jurisdiction. Class action and collective action waivers. Confidentiality of arbitration that prevents the library from sharing information about disputes with peers.</t>
   </si>
   <si>
-    <t>Section 8.2</t>
+    <t>Section 7.2 (Dispute Resolution Procedures)</t>
   </si>
   <si>
     <t xml:space="preserve">  Governance and Change Management</t>
@@ -1113,7 +1066,7 @@
     <t>Hyperlinks anywhere in the agreement to documents not attached. Acceptable Use Policy, Privacy Policy, or Service Terms referenced without copies attached. Update mechanisms that give no termination right for objections. Vendor-side update rights paired with automatic renewal. Click-through requirements imposed on patrons at point of use.</t>
   </si>
   <si>
-    <t>Section 9.1</t>
+    <t>Section 8.1 (Amendment and Incorporation)</t>
   </si>
   <si>
     <t>GC-NO</t>
@@ -1140,7 +1093,7 @@
     <t>Asymmetric notice mechanisms (vendor by posting, licensee by certified mail). Notice effective without actual receipt. No requirement to update notice contacts. Notice to email addresses that are not specifically designated. Notice provisions that exempt 'operational communications' from formal notice requirements.</t>
   </si>
   <si>
-    <t>Section 9.2</t>
+    <t>Section 8.2 (Notices, Audits, and Integration)</t>
   </si>
   <si>
     <t>GC-AR</t>
@@ -1167,9 +1120,6 @@
     <t>Audit rights extending beyond use of the Licensed Content. Multiple audits per year permitted. No notice requirement. Licensee-borne costs regardless of findings. Audit rights extending to parties not in direct privity. No carve-out for protected patron information.</t>
   </si>
   <si>
-    <t>Section 9.3</t>
-  </si>
-  <si>
     <t>GC-EA</t>
   </si>
   <si>
@@ -1194,20 +1144,20 @@
     <t>Vendor policies stated to control in any conflict. Broad incorporation of website-available policies. No clear order of precedence among the agreement, exhibits, and external documents. References to 'Licensor's standard terms' or similar without identification.</t>
   </si>
   <si>
-    <t>Section 9.4</t>
-  </si>
-  <si>
     <t>Theme Index</t>
   </si>
   <si>
     <t>A quick reference to clauses organized by thematic group. Use the Clause ID to find each clause in the Clause Bank tab.</t>
+  </si>
+  <si>
+    <t>Last updated: July 14, 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1278,6 +1228,12 @@
       <sz val="11"/>
       <color rgb="FF5D6D7E"/>
       <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="24">
@@ -1425,7 +1381,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1585,6 +1541,7 @@
     <xf numFmtId="0" fontId="0" fillId="23" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1625,6 +1582,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1912,211 +1873,223 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A49"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="120" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1" ht="26.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+    <row r="3" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2"/>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="57" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" s="57"/>
+    </row>
+    <row r="6" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="90" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="7" spans="1:1" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+    <row r="9" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+    <row r="10" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+    <row r="11" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+    <row r="12" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+    <row r="13" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+    <row r="16" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+    <row r="19" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+    <row r="20" spans="1:1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+    <row r="21" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+    <row r="24" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
+    <row r="27" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+    <row r="28" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+    <row r="29" spans="1:1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+    <row r="30" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+    <row r="31" spans="1:1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
+    <row r="33" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="105" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+    <row r="34" spans="1:1" ht="105" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
+    <row r="36" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="35" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
+    <row r="37" spans="1:1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A37" s="3" t="s">
+    <row r="39" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="38" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+    <row r="40" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:1" ht="90" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+    <row r="41" spans="1:1" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+    <row r="42" spans="1:1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
+    <row r="43" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
+    <row r="45" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
+    <row r="46" spans="1:1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A48" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" s="5" t="s">
         <v>37</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -2124,14 +2097,14 @@
     <col min="5" max="7" width="48" customWidth="1"/>
     <col min="8" max="8" width="40" customWidth="1"/>
     <col min="9" max="9" width="36" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="10" max="10" width="46" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
     <col min="13" max="14" width="13" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>38</v>
       </c>
@@ -2178,26 +2151,26 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="61" t="s">
+    <row r="2" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-    </row>
-    <row r="3" spans="1:15" ht="300" x14ac:dyDescent="0.25">
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+    </row>
+    <row r="3" spans="1:15" ht="300" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>54</v>
       </c>
@@ -2236,7 +2209,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="240" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="240" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>65</v>
       </c>
@@ -2277,7 +2250,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="195" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="195" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>74</v>
       </c>
@@ -2306,7 +2279,7 @@
         <v>80</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="K5" s="13"/>
       <c r="L5" s="14" t="s">
@@ -2318,36 +2291,36 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="180" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="180" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>56</v>
       </c>
       <c r="D6" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="G6" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="H6" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="I6" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="J6" s="12" t="s">
         <v>89</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>90</v>
       </c>
       <c r="K6" s="14" t="s">
         <v>64</v>
@@ -2361,36 +2334,36 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="165" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="165" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>92</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>56</v>
       </c>
       <c r="D7" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="F7" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="G7" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="H7" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="I7" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="I7" s="12" t="s">
-        <v>98</v>
-      </c>
       <c r="J7" s="12" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="K7" s="13"/>
       <c r="L7" s="13"/>
@@ -2400,36 +2373,36 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="210" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="210" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>56</v>
       </c>
       <c r="D8" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="G8" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="H8" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="I8" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="J8" s="12" t="s">
         <v>106</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>108</v>
       </c>
       <c r="K8" s="13"/>
       <c r="L8" s="13"/>
@@ -2439,36 +2412,36 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="375" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="375" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>56</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E9" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="G9" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="H9" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="I9" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="H9" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>115</v>
-      </c>
       <c r="J9" s="12" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="K9" s="13"/>
       <c r="L9" s="14" t="s">
@@ -2482,36 +2455,36 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="315" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="315" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>56</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E10" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="H10" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="I10" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G10" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>123</v>
-      </c>
       <c r="J10" s="12" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="K10" s="13"/>
       <c r="L10" s="14" t="s">
@@ -2525,36 +2498,36 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="225" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="225" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>56</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E11" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="I11" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>131</v>
-      </c>
       <c r="J11" s="12" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="K11" s="14" t="s">
         <v>64</v>
@@ -2564,55 +2537,55 @@
       <c r="N11" s="13"/>
       <c r="O11" s="13"/>
     </row>
-    <row r="12" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="57" t="s">
+    <row r="12" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="B12" s="59"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="59"/>
+      <c r="K12" s="59"/>
+      <c r="L12" s="59"/>
+      <c r="M12" s="59"/>
+      <c r="N12" s="59"/>
+      <c r="O12" s="59"/>
+    </row>
+    <row r="13" spans="1:15" ht="300" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B12" s="58"/>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="58"/>
-      <c r="K12" s="58"/>
-      <c r="L12" s="58"/>
-      <c r="M12" s="58"/>
-      <c r="N12" s="58"/>
-      <c r="O12" s="58"/>
-    </row>
-    <row r="13" spans="1:15" ht="300" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="F13" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="G13" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="H13" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="I13" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="J13" s="12" t="s">
         <v>138</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>143</v>
       </c>
       <c r="K13" s="15" t="s">
         <v>73</v>
@@ -2624,36 +2597,36 @@
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
     </row>
-    <row r="14" spans="1:15" ht="225" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="225" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="G14" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="H14" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D14" s="8" t="s">
+      <c r="I14" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="J14" s="12" t="s">
         <v>147</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>152</v>
       </c>
       <c r="K14" s="13"/>
       <c r="L14" s="15" t="s">
@@ -2665,36 +2638,36 @@
       </c>
       <c r="O14" s="13"/>
     </row>
-    <row r="15" spans="1:15" ht="210" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="210" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="G15" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="H15" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D15" s="8" t="s">
+      <c r="I15" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="E15" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>160</v>
-      </c>
       <c r="J15" s="12" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="K15" s="14" t="s">
         <v>64</v>
@@ -2706,36 +2679,36 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13"/>
     </row>
-    <row r="16" spans="1:15" ht="240" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="240" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="H16" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="I16" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>169</v>
-      </c>
       <c r="J16" s="12" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="K16" s="14" t="s">
         <v>64</v>
@@ -2749,36 +2722,36 @@
       </c>
       <c r="O16" s="13"/>
     </row>
-    <row r="17" spans="1:15" ht="180" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" ht="180" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="I17" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="B17" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="I17" s="12" t="s">
-        <v>178</v>
-      </c>
       <c r="J17" s="12" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="K17" s="13"/>
       <c r="L17" s="14" t="s">
@@ -2792,55 +2765,55 @@
       </c>
       <c r="O17" s="13"/>
     </row>
-    <row r="18" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="65" t="s">
+    <row r="18" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="66" t="s">
+        <v>172</v>
+      </c>
+      <c r="B18" s="59"/>
+      <c r="C18" s="59"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="59"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="59"/>
+      <c r="J18" s="59"/>
+      <c r="K18" s="59"/>
+      <c r="L18" s="59"/>
+      <c r="M18" s="59"/>
+      <c r="N18" s="59"/>
+      <c r="O18" s="59"/>
+    </row>
+    <row r="19" spans="1:15" ht="225" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="H19" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="B18" s="58"/>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="58"/>
-      <c r="J18" s="58"/>
-      <c r="K18" s="58"/>
-      <c r="L18" s="58"/>
-      <c r="M18" s="58"/>
-      <c r="N18" s="58"/>
-      <c r="O18" s="58"/>
-    </row>
-    <row r="19" spans="1:15" ht="225" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+      <c r="I19" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="J19" s="12" t="s">
         <v>182</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="H19" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="I19" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="J19" s="12" t="s">
-        <v>190</v>
       </c>
       <c r="K19" s="13"/>
       <c r="L19" s="14" t="s">
@@ -2850,36 +2823,36 @@
       <c r="N19" s="13"/>
       <c r="O19" s="13"/>
     </row>
-    <row r="20" spans="1:15" ht="195" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" ht="195" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="J20" s="12" t="s">
         <v>191</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="H20" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="I20" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="J20" s="12" t="s">
-        <v>199</v>
       </c>
       <c r="K20" s="13"/>
       <c r="L20" s="14" t="s">
@@ -2889,36 +2862,36 @@
       <c r="N20" s="13"/>
       <c r="O20" s="13"/>
     </row>
-    <row r="21" spans="1:15" ht="210" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" ht="210" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="17" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="K21" s="13"/>
       <c r="L21" s="13"/>
@@ -2926,55 +2899,55 @@
       <c r="N21" s="13"/>
       <c r="O21" s="13"/>
     </row>
-    <row r="22" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="64" t="s">
+    <row r="22" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="65" t="s">
+        <v>200</v>
+      </c>
+      <c r="B22" s="59"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="59"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="59"/>
+      <c r="J22" s="59"/>
+      <c r="K22" s="59"/>
+      <c r="L22" s="59"/>
+      <c r="M22" s="59"/>
+      <c r="N22" s="59"/>
+      <c r="O22" s="59"/>
+    </row>
+    <row r="23" spans="1:15" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="H23" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="B22" s="58"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="58"/>
-      <c r="K22" s="58"/>
-      <c r="L22" s="58"/>
-      <c r="M22" s="58"/>
-      <c r="N22" s="58"/>
-      <c r="O22" s="58"/>
-    </row>
-    <row r="23" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
+      <c r="I23" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="J23" s="12" t="s">
         <v>210</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="H23" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="I23" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="J23" s="12" t="s">
-        <v>218</v>
       </c>
       <c r="K23" s="13"/>
       <c r="L23" s="14" t="s">
@@ -2986,36 +2959,36 @@
       <c r="N23" s="13"/>
       <c r="O23" s="13"/>
     </row>
-    <row r="24" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="J24" s="12" t="s">
         <v>219</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="G24" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="I24" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="J24" s="12" t="s">
-        <v>227</v>
       </c>
       <c r="K24" s="13"/>
       <c r="L24" s="14" t="s">
@@ -3027,36 +3000,36 @@
       <c r="N24" s="13"/>
       <c r="O24" s="13"/>
     </row>
-    <row r="25" spans="1:15" ht="180" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" ht="180" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="18" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="K25" s="14" t="s">
         <v>64</v>
@@ -3070,102 +3043,102 @@
       <c r="N25" s="13"/>
       <c r="O25" s="13"/>
     </row>
-    <row r="26" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="59" t="s">
+    <row r="26" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="60" t="s">
+        <v>228</v>
+      </c>
+      <c r="B26" s="59"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="59"/>
+      <c r="E26" s="59"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="59"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="59"/>
+      <c r="K26" s="59"/>
+      <c r="L26" s="59"/>
+      <c r="M26" s="59"/>
+      <c r="N26" s="59"/>
+      <c r="O26" s="59"/>
+    </row>
+    <row r="27" spans="1:15" ht="225" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="I27" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="B26" s="58"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
-      <c r="J26" s="58"/>
-      <c r="K26" s="58"/>
-      <c r="L26" s="58"/>
-      <c r="M26" s="58"/>
-      <c r="N26" s="58"/>
-      <c r="O26" s="58"/>
-    </row>
-    <row r="27" spans="1:15" ht="225" x14ac:dyDescent="0.25">
-      <c r="A27" s="19" t="s">
+      <c r="J27" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="K27" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="L27" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="M27" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="N27" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="O27" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="225" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="B28" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="C28" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="E28" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="F28" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="G28" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="G27" s="11" t="s">
+      <c r="H28" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="H27" s="12" t="s">
+      <c r="I28" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="I27" s="12" t="s">
+      <c r="J28" s="12" t="s">
         <v>246</v>
-      </c>
-      <c r="J27" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="K27" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="L27" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="M27" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="N27" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="O27" s="14" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" ht="225" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="G28" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="H28" s="12" t="s">
-        <v>253</v>
-      </c>
-      <c r="I28" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="J28" s="12" t="s">
-        <v>255</v>
       </c>
       <c r="K28" s="13"/>
       <c r="L28" s="14" t="s">
@@ -3181,36 +3154,36 @@
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="330" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" ht="330" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="19" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="K29" s="13"/>
       <c r="L29" s="14" t="s">
@@ -3222,36 +3195,36 @@
       <c r="N29" s="13"/>
       <c r="O29" s="13"/>
     </row>
-    <row r="30" spans="1:15" ht="195" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" ht="195" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="19" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="K30" s="13"/>
       <c r="L30" s="13"/>
@@ -3261,36 +3234,36 @@
       <c r="N30" s="13"/>
       <c r="O30" s="13"/>
     </row>
-    <row r="31" spans="1:15" ht="270" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" ht="270" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="19" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="K31" s="13"/>
       <c r="L31" s="14" t="s">
@@ -3300,36 +3273,36 @@
       <c r="N31" s="13"/>
       <c r="O31" s="13"/>
     </row>
-    <row r="32" spans="1:15" ht="165" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" ht="165" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="19" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>289</v>
+        <v>262</v>
       </c>
       <c r="K32" s="13"/>
       <c r="L32" s="13"/>
@@ -3337,55 +3310,55 @@
       <c r="N32" s="13"/>
       <c r="O32" s="13"/>
     </row>
-    <row r="33" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="63" t="s">
-        <v>290</v>
-      </c>
-      <c r="B33" s="58"/>
-      <c r="C33" s="58"/>
-      <c r="D33" s="58"/>
-      <c r="E33" s="58"/>
-      <c r="F33" s="58"/>
-      <c r="G33" s="58"/>
-      <c r="H33" s="58"/>
-      <c r="I33" s="58"/>
-      <c r="J33" s="58"/>
-      <c r="K33" s="58"/>
-      <c r="L33" s="58"/>
-      <c r="M33" s="58"/>
-      <c r="N33" s="58"/>
-      <c r="O33" s="58"/>
-    </row>
-    <row r="34" spans="1:15" ht="180" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="64" t="s">
+        <v>278</v>
+      </c>
+      <c r="B33" s="59"/>
+      <c r="C33" s="59"/>
+      <c r="D33" s="59"/>
+      <c r="E33" s="59"/>
+      <c r="F33" s="59"/>
+      <c r="G33" s="59"/>
+      <c r="H33" s="59"/>
+      <c r="I33" s="59"/>
+      <c r="J33" s="59"/>
+      <c r="K33" s="59"/>
+      <c r="L33" s="59"/>
+      <c r="M33" s="59"/>
+      <c r="N33" s="59"/>
+      <c r="O33" s="59"/>
+    </row>
+    <row r="34" spans="1:15" ht="180" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="20" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="K34" s="13"/>
       <c r="L34" s="14" t="s">
@@ -3395,81 +3368,81 @@
       <c r="N34" s="13"/>
       <c r="O34" s="13"/>
     </row>
-    <row r="35" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="H35" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="J35" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="K35" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="L35" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="M35" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="N35" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="O35" s="13"/>
+    </row>
+    <row r="36" spans="1:15" ht="210" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="G36" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="H36" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="B35" s="20" t="s">
+      <c r="I36" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="C35" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="H35" s="12" t="s">
-        <v>306</v>
-      </c>
-      <c r="I35" s="12" t="s">
-        <v>307</v>
-      </c>
-      <c r="J35" s="12" t="s">
-        <v>308</v>
-      </c>
-      <c r="K35" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="L35" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="M35" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="N35" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="O35" s="13"/>
-    </row>
-    <row r="36" spans="1:15" ht="210" x14ac:dyDescent="0.25">
-      <c r="A36" s="20" t="s">
-        <v>309</v>
-      </c>
-      <c r="B36" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="F36" s="10" t="s">
-        <v>312</v>
-      </c>
-      <c r="G36" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="H36" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="I36" s="12" t="s">
-        <v>315</v>
-      </c>
       <c r="J36" s="12" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
       <c r="K36" s="14" t="s">
         <v>64</v>
@@ -3481,36 +3454,36 @@
       <c r="N36" s="13"/>
       <c r="O36" s="13"/>
     </row>
-    <row r="37" spans="1:15" ht="240" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" ht="240" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="20" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="K37" s="14" t="s">
         <v>64</v>
@@ -3526,55 +3499,55 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="60" t="s">
-        <v>326</v>
-      </c>
-      <c r="B38" s="58"/>
-      <c r="C38" s="58"/>
-      <c r="D38" s="58"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="58"/>
-      <c r="G38" s="58"/>
-      <c r="H38" s="58"/>
-      <c r="I38" s="58"/>
-      <c r="J38" s="58"/>
-      <c r="K38" s="58"/>
-      <c r="L38" s="58"/>
-      <c r="M38" s="58"/>
-      <c r="N38" s="58"/>
-      <c r="O38" s="58"/>
-    </row>
-    <row r="39" spans="1:15" ht="180" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="61" t="s">
+        <v>312</v>
+      </c>
+      <c r="B38" s="59"/>
+      <c r="C38" s="59"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="59"/>
+      <c r="G38" s="59"/>
+      <c r="H38" s="59"/>
+      <c r="I38" s="59"/>
+      <c r="J38" s="59"/>
+      <c r="K38" s="59"/>
+      <c r="L38" s="59"/>
+      <c r="M38" s="59"/>
+      <c r="N38" s="59"/>
+      <c r="O38" s="59"/>
+    </row>
+    <row r="39" spans="1:15" ht="180" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="21" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="K39" s="13"/>
       <c r="L39" s="14" t="s">
@@ -3590,36 +3563,36 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="195" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" ht="195" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="21" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="C40" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="G40" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="H40" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="I40" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="J40" s="12" t="s">
         <v>330</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="F40" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="G40" s="11" t="s">
-        <v>341</v>
-      </c>
-      <c r="H40" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="I40" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="J40" s="12" t="s">
-        <v>344</v>
       </c>
       <c r="K40" s="13"/>
       <c r="L40" s="14" t="s">
@@ -3635,102 +3608,102 @@
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="62" t="s">
+    <row r="41" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="63" t="s">
+        <v>331</v>
+      </c>
+      <c r="B41" s="59"/>
+      <c r="C41" s="59"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="59"/>
+      <c r="F41" s="59"/>
+      <c r="G41" s="59"/>
+      <c r="H41" s="59"/>
+      <c r="I41" s="59"/>
+      <c r="J41" s="59"/>
+      <c r="K41" s="59"/>
+      <c r="L41" s="59"/>
+      <c r="M41" s="59"/>
+      <c r="N41" s="59"/>
+      <c r="O41" s="59"/>
+    </row>
+    <row r="42" spans="1:15" ht="210" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="22" t="s">
+        <v>332</v>
+      </c>
+      <c r="B42" s="22" t="s">
+        <v>333</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="I42" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="J42" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="K42" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="L42" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="M42" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="N42" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="O42" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="180" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="B43" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="E43" s="9" t="s">
         <v>345</v>
       </c>
-      <c r="B41" s="58"/>
-      <c r="C41" s="58"/>
-      <c r="D41" s="58"/>
-      <c r="E41" s="58"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="58"/>
-      <c r="H41" s="58"/>
-      <c r="I41" s="58"/>
-      <c r="J41" s="58"/>
-      <c r="K41" s="58"/>
-      <c r="L41" s="58"/>
-      <c r="M41" s="58"/>
-      <c r="N41" s="58"/>
-      <c r="O41" s="58"/>
-    </row>
-    <row r="42" spans="1:15" ht="210" x14ac:dyDescent="0.25">
-      <c r="A42" s="22" t="s">
+      <c r="F43" s="10" t="s">
         <v>346</v>
       </c>
-      <c r="B42" s="22" t="s">
+      <c r="G43" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="H43" s="12" t="s">
         <v>348</v>
       </c>
-      <c r="D42" s="8" t="s">
+      <c r="I43" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="E42" s="9" t="s">
+      <c r="J43" s="12" t="s">
         <v>350</v>
-      </c>
-      <c r="F42" s="10" t="s">
-        <v>351</v>
-      </c>
-      <c r="G42" s="11" t="s">
-        <v>352</v>
-      </c>
-      <c r="H42" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="I42" s="12" t="s">
-        <v>354</v>
-      </c>
-      <c r="J42" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="K42" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="L42" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="M42" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="N42" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="O42" s="14" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" ht="180" x14ac:dyDescent="0.25">
-      <c r="A43" s="22" t="s">
-        <v>356</v>
-      </c>
-      <c r="B43" s="22" t="s">
-        <v>357</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="F43" s="10" t="s">
-        <v>360</v>
-      </c>
-      <c r="G43" s="11" t="s">
-        <v>361</v>
-      </c>
-      <c r="H43" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="I43" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="J43" s="12" t="s">
-        <v>364</v>
       </c>
       <c r="K43" s="13"/>
       <c r="L43" s="14" t="s">
@@ -3742,36 +3715,36 @@
       <c r="N43" s="13"/>
       <c r="O43" s="13"/>
     </row>
-    <row r="44" spans="1:15" ht="210" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" ht="210" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="22" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="J44" s="12" t="s">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="K44" s="13"/>
       <c r="L44" s="13"/>
@@ -3783,36 +3756,36 @@
         <v>64</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="195" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" ht="195" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="22" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="I45" s="12" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>382</v>
+        <v>350</v>
       </c>
       <c r="K45" s="14" t="s">
         <v>64</v>
@@ -3843,13 +3816,14 @@
     <mergeCell ref="A18:O18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D40"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -3857,17 +3831,17 @@
     <col min="4" max="4" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="23" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>40</v>
       </c>
@@ -3881,7 +3855,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="25" t="s">
         <v>56</v>
       </c>
@@ -3895,7 +3869,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="28"/>
       <c r="B6" s="25" t="s">
         <v>65</v>
@@ -3907,7 +3881,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="28"/>
       <c r="B7" s="25" t="s">
         <v>74</v>
@@ -3919,417 +3893,418 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="28"/>
       <c r="B8" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="D8" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="D8" s="27" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="28"/>
       <c r="B9" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="D9" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="D9" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="28"/>
       <c r="B10" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="C10" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="28"/>
       <c r="B11" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="28"/>
       <c r="B12" s="25" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="28"/>
       <c r="B13" s="25" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="29" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B14" s="29" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="32"/>
       <c r="B15" s="29" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C15" s="30" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="32"/>
       <c r="B16" s="29" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C16" s="30" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="32"/>
       <c r="B17" s="29" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="32"/>
       <c r="B18" s="29" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C18" s="30" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D18" s="31" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="B19" s="33" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="33" t="s">
-        <v>183</v>
-      </c>
-      <c r="B19" s="33" t="s">
-        <v>181</v>
-      </c>
       <c r="C19" s="34" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="D19" s="35" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="36"/>
       <c r="B20" s="33" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="D20" s="35" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="36"/>
       <c r="B21" s="33" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C21" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="D21" s="35" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="B22" s="37" t="s">
         <v>201</v>
       </c>
-      <c r="D21" s="35" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="37" t="s">
-        <v>211</v>
-      </c>
-      <c r="B22" s="37" t="s">
-        <v>209</v>
-      </c>
       <c r="C22" s="38" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="40"/>
       <c r="B23" s="37" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="40"/>
       <c r="B24" s="37" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C24" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="D24" s="39" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="41" t="s">
+        <v>231</v>
+      </c>
+      <c r="B25" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="D24" s="39" t="s">
+      <c r="C25" s="42" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="41" t="s">
-        <v>240</v>
-      </c>
-      <c r="B25" s="41" t="s">
-        <v>238</v>
-      </c>
-      <c r="C25" s="42" t="s">
-        <v>239</v>
-      </c>
       <c r="D25" s="43" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="44"/>
       <c r="B26" s="41" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="C26" s="42" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="D26" s="43" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="44"/>
       <c r="B27" s="41" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C27" s="42" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="D27" s="43" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="44"/>
       <c r="B28" s="41" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="D28" s="43" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="44"/>
       <c r="B29" s="41" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="C29" s="42" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="D29" s="43" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="44"/>
       <c r="B30" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="C30" s="42" t="s">
+        <v>271</v>
+      </c>
+      <c r="D30" s="43" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="45" t="s">
         <v>281</v>
       </c>
-      <c r="C30" s="42" t="s">
+      <c r="B31" s="45" t="s">
+        <v>279</v>
+      </c>
+      <c r="C31" s="46" t="s">
+        <v>280</v>
+      </c>
+      <c r="D31" s="47" t="s">
         <v>282</v>
       </c>
-      <c r="D30" s="43" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="45" t="s">
-        <v>293</v>
-      </c>
-      <c r="B31" s="45" t="s">
-        <v>291</v>
-      </c>
-      <c r="C31" s="46" t="s">
-        <v>292</v>
-      </c>
-      <c r="D31" s="47" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="48"/>
       <c r="B32" s="45" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="C32" s="46" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="D32" s="47" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="48"/>
       <c r="B33" s="45" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="C33" s="46" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="D33" s="47" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="48"/>
       <c r="B34" s="45" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="C34" s="46" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="D34" s="47" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="49" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="B35" s="49" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="C35" s="50" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="D35" s="51" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="52"/>
       <c r="B36" s="49" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="C36" s="50" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="D36" s="51" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="53" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="B37" s="53" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="C37" s="54" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="D37" s="55" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="56"/>
       <c r="B38" s="53" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="C38" s="54" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="D38" s="55" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="56"/>
       <c r="B39" s="53" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="C39" s="54" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="D39" s="55" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="56"/>
       <c r="B40" s="53" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="C40" s="54" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="D40" s="55" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>